--- a/docs/printer_statistics_2026-10-07/printer_statistics_2026-10-07.xlsx
+++ b/docs/printer_statistics_2026-10-07/printer_statistics_2026-10-07.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yawllen\Documents\printer-statistics\2026-10-07_17-05-54\_excel-authoring\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yawllen\Documents\GitHub\Nir2\docs\printer_statistics_2026-10-07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{57C1C3B2-BB93-42D4-A849-27D4AE3AAA48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEB785C0-8251-46AB-86E4-B86695F43649}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{1A8FC01A-C03A-40E8-A956-EC18ED2B42BD}"/>
   </bookViews>
@@ -16,6 +16,10 @@
     <sheet name="Сводная статистика" sheetId="2" r:id="rId1"/>
     <sheet name="Данные принтеров" sheetId="1" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">'Сводная статистика'!$X$2:$X$7</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'Сводная статистика'!$Y$2:$Y$7</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -251,7 +255,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,21 +266,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="204"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -295,6 +284,29 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
     </font>
@@ -331,11 +343,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -345,31 +354,49 @@
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -410,16 +437,33 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1650" b="0">
-                <a:latin typeface="Arial"/>
-                <a:ea typeface="Arial"/>
-                <a:cs typeface="Arial"/>
+              <a:defRPr sz="1800" b="0">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="ru-RU"/>
-              <a:t>Количество</a:t>
+              <a:rPr lang="ru-RU" sz="1800">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>Статистика</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="ru-RU" sz="1800" baseline="0">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t> печатей на ферме</a:t>
+            </a:r>
+            <a:endParaRPr lang="ru-RU" sz="1800">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:endParaRPr>
           </a:p>
         </c:rich>
       </c:tx>
@@ -427,8 +471,18 @@
     </c:title>
     <c:autoTitleDeleted val="0"/>
     <c:plotArea>
-      <c:layout/>
-      <c:pieChart>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.3523759532060297E-2"/>
+          <c:y val="0.17487844068148015"/>
+          <c:w val="0.50320572092021254"/>
+          <c:h val="0.77929282690123625"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:doughnutChart>
         <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
@@ -439,21 +493,12 @@
           <c:dPt>
             <c:idx val="0"/>
             <c:bubble3D val="0"/>
+            <c:explosion val="13"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="FEC820"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
               <a:effectLst/>
-              <a:extLst>
-                <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                  <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                    <a:noFill/>
-                  </a14:hiddenLine>
-                </a:ext>
-              </a:extLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -468,17 +513,7 @@
               <a:solidFill>
                 <a:srgbClr val="66C76A"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
               <a:effectLst/>
-              <a:extLst>
-                <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                  <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                    <a:noFill/>
-                  </a14:hiddenLine>
-                </a:ext>
-              </a:extLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -493,17 +528,7 @@
               <a:solidFill>
                 <a:srgbClr val="A44646"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
               <a:effectLst/>
-              <a:extLst>
-                <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                  <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                    <a:noFill/>
-                  </a14:hiddenLine>
-                </a:ext>
-              </a:extLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -518,17 +543,7 @@
               <a:solidFill>
                 <a:srgbClr val="FF6363"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
               <a:effectLst/>
-              <a:extLst>
-                <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                  <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                    <a:noFill/>
-                  </a14:hiddenLine>
-                </a:ext>
-              </a:extLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -543,17 +558,7 @@
               <a:solidFill>
                 <a:srgbClr val="5E2F2F"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
               <a:effectLst/>
-              <a:extLst>
-                <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                  <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                    <a:noFill/>
-                  </a14:hiddenLine>
-                </a:ext>
-              </a:extLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -568,17 +573,7 @@
               <a:solidFill>
                 <a:srgbClr val="A3A3A3"/>
               </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
               <a:effectLst/>
-              <a:extLst>
-                <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                  <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-                    <a:noFill/>
-                  </a14:hiddenLine>
-                </a:ext>
-              </a:extLst>
             </c:spPr>
             <c:extLst>
               <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -586,6 +581,9 @@
               </c:ext>
             </c:extLst>
           </c:dPt>
+          <c:dLbls>
+            <c:delete val="1"/>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'Сводная статистика'!$X$2:$X$7</c:f>
@@ -652,10 +650,11 @@
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showLeaderLines val="1"/>
+          <c:showLeaderLines val="0"/>
         </c:dLbls>
         <c:firstSliceAng val="0"/>
-      </c:pieChart>
+        <c:holeSize val="50"/>
+      </c:doughnutChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -668,26 +667,31 @@
               <a:noFill/>
             </a14:hiddenFill>
           </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:noFill/>
-            </a14:hiddenLine>
-          </a:ext>
         </a:extLst>
       </c:spPr>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.62837785882372377"/>
+          <c:y val="0.17230094354044509"/>
+          <c:w val="0.28885444542097821"/>
+          <c:h val="0.75777694234109039"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:txPr>
         <a:bodyPr/>
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1000">
-              <a:latin typeface="Arial"/>
-              <a:ea typeface="Arial"/>
-              <a:cs typeface="Arial"/>
+            <a:defRPr sz="1800">
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="ru-RU"/>
@@ -720,6 +724,7 @@
     <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
+  <c:userShapes r:id="rId1"/>
 </c:chartSpace>
 </file>
 
@@ -728,15 +733,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>489090</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>285750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>622300</xdr:colOff>
+      <xdr:colOff>491331</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
+      <xdr:rowOff>178594</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -762,6 +767,177 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.44789</cdr:x>
+      <cdr:y>0.27481</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.60103</cdr:x>
+      <cdr:y>0.43185</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="2" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{168AB649-72F9-D23E-F765-AF87FD4444C3}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="2114409" y="837712"/>
+          <a:ext cx="722924" cy="478692"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" vertOverflow="clip" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="ru-RU" sz="2000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>27%</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.14527</cdr:x>
+      <cdr:y>0.69769</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.29372</cdr:x>
+      <cdr:y>0.85472</cdr:y>
+    </cdr:to>
+    <cdr:sp macro="" textlink="">
+      <cdr:nvSpPr>
+        <cdr:cNvPr id="3" name="TextBox 1">
+          <a:extLst xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{933A1654-4165-6B20-2906-59312F3114D7}"/>
+            </a:ext>
+          </a:extLst>
+        </cdr:cNvPr>
+        <cdr:cNvSpPr txBox="1"/>
+      </cdr:nvSpPr>
+      <cdr:spPr>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:off x="685800" y="2126761"/>
+          <a:ext cx="700802" cy="478692"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </cdr:spPr>
+      <cdr:txBody>
+        <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" wrap="square" rtlCol="0"/>
+        <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:lvl1pPr marL="0" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl1pPr>
+          <a:lvl2pPr marL="457200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl2pPr>
+          <a:lvl3pPr marL="914400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl3pPr>
+          <a:lvl4pPr marL="1371600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl4pPr>
+          <a:lvl5pPr marL="1828800" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl5pPr>
+          <a:lvl6pPr marL="2286000" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl6pPr>
+          <a:lvl7pPr marL="2743200" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl7pPr>
+          <a:lvl8pPr marL="3200400" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl8pPr>
+          <a:lvl9pPr marL="3657600" indent="0">
+            <a:defRPr sz="1100">
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:lvl9pPr>
+        </a:lstStyle>
+        <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:r>
+            <a:rPr lang="ru-RU" sz="2000" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="Calibri" panose="020F0502020204030204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:rPr>
+            <a:t>66%</a:t>
+          </a:r>
+        </a:p>
+      </cdr:txBody>
+    </cdr:sp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1082,152 +1258,152 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EB46875-0738-40A3-AC28-E89EB3D22948}">
   <dimension ref="A2:Y28"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="23.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="49.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36.6328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.6328125" style="1" customWidth="1"/>
-    <col min="5" max="14" width="9.6328125" style="1" customWidth="1"/>
-    <col min="15" max="23" width="8.7265625" style="1"/>
-    <col min="24" max="26" width="0" style="1" hidden="1" customWidth="1"/>
-    <col min="27" max="16384" width="8.7265625" style="1"/>
+    <col min="1" max="1" width="49.6328125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="36.6328125" style="11" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="3.6328125" style="11" customWidth="1"/>
+    <col min="5" max="14" width="9.6328125" style="11" customWidth="1"/>
+    <col min="15" max="23" width="8.7265625" style="11"/>
+    <col min="24" max="26" width="0" style="11" hidden="1" customWidth="1"/>
+    <col min="27" max="16384" width="8.7265625" style="11"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:25" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="X2" s="1" t="str">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="X2" s="11" t="str">
         <f>A17</f>
         <v>Отменено</v>
       </c>
-      <c r="Y2" s="4">
+      <c r="Y2" s="12">
         <f>B17</f>
         <v>1237</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="X3" s="1" t="str">
+      <c r="B3" s="10"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="X3" s="11" t="str">
         <f>A16</f>
         <v>Завершено</v>
       </c>
-      <c r="Y3" s="4">
+      <c r="Y3" s="12">
         <f>B16</f>
         <v>3063</v>
       </c>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="X4" s="1" t="str">
-        <f>A18</f>
+      <c r="X4" s="11" t="str">
+        <f t="shared" ref="X4:Y7" si="0">A18</f>
         <v>Аварийная остановка</v>
       </c>
-      <c r="Y4" s="4">
-        <f>B18</f>
+      <c r="Y4" s="12">
+        <f t="shared" si="0"/>
         <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="X5" s="1" t="str">
-        <f>A19</f>
+      <c r="X5" s="11" t="str">
+        <f t="shared" si="0"/>
         <v>Ошибка</v>
       </c>
-      <c r="Y5" s="4">
-        <f>B19</f>
+      <c r="Y5" s="12">
+        <f t="shared" si="0"/>
         <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="X6" s="1" t="str">
-        <f>A20</f>
+      <c r="X6" s="11" t="str">
+        <f t="shared" si="0"/>
         <v>Ошибка системы</v>
       </c>
-      <c r="Y6" s="4">
-        <f>B20</f>
+      <c r="Y6" s="12">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="11">
         <f>COUNTA('Данные принтеров'!A2:A11)</f>
         <v>10</v>
       </c>
-      <c r="X7" s="1" t="str">
-        <f>A21</f>
+      <c r="X7" s="11" t="str">
+        <f t="shared" si="0"/>
         <v>Неудачно</v>
       </c>
-      <c r="Y7" s="4">
-        <f>B21</f>
+      <c r="Y7" s="12">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="1" t="str">
+      <c r="B8" s="11" t="str">
         <f>INT(ROUND('Данные принтеров'!C14,0)/86400)&amp;" д "&amp;INT(MOD(ROUND('Данные принтеров'!C14,0),86400)/3600)&amp;" ч "&amp;INT(MOD(ROUND('Данные принтеров'!C14,0),3600)/60)&amp;" мин "&amp;MOD(ROUND('Данные принтеров'!C14,0),60)&amp;" с"</f>
         <v>765 д 7 ч 38 мин 21 с</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="B9" s="1" t="str">
+      <c r="B9" s="11" t="str">
         <f>INT(ROUND('Данные принтеров'!D14,0)/86400)&amp;" д "&amp;INT(MOD(ROUND('Данные принтеров'!D14,0),86400)/3600)&amp;" ч "&amp;INT(MOD(ROUND('Данные принтеров'!D14,0),3600)/60)&amp;" мин "&amp;MOD(ROUND('Данные принтеров'!D14,0),60)&amp;" с"</f>
         <v>4 д 17 ч 17 мин 21 с</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="B10" s="1" t="str">
+      <c r="B10" s="11" t="str">
         <f>INT(ROUND('Данные принтеров'!C14/'Данные принтеров'!F14,0)/3600)&amp;" ч "&amp;INT(MOD(ROUND('Данные принтеров'!C14/'Данные принтеров'!F14,0),3600)/60)&amp;" мин "&amp;MOD(ROUND('Данные принтеров'!C14/'Данные принтеров'!F14,0),60)&amp;" с"</f>
         <v>3 ч 56 мин 8 с</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="14">
         <f>ROUND('Данные принтеров'!E14/1000,1)</f>
         <v>51760.1</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="12">
         <f>'Данные принтеров'!F14</f>
         <v>4667</v>
       </c>
@@ -1235,157 +1411,157 @@
     <row r="13" spans="1:25" ht="25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="14" spans="1:25" ht="25" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="15" spans="1:25" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="13" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16" s="12">
         <f>'Данные принтеров'!H14</f>
         <v>3063</v>
       </c>
-      <c r="C16" s="6">
-        <f>B16/$B$22</f>
+      <c r="C16" s="15">
+        <f t="shared" ref="C16:C21" si="1">B16/$B$22</f>
         <v>0.66012931034482758</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="4">
+      <c r="B17" s="12">
         <f>'Данные принтеров'!I14</f>
         <v>1237</v>
       </c>
-      <c r="C17" s="6">
-        <f>B17/$B$22</f>
+      <c r="C17" s="15">
+        <f t="shared" si="1"/>
         <v>0.2665948275862069</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18" s="12">
         <f>'Данные принтеров'!J14</f>
         <v>244</v>
       </c>
-      <c r="C18" s="6">
-        <f>B18/$B$22</f>
+      <c r="C18" s="15">
+        <f t="shared" si="1"/>
         <v>5.2586206896551725E-2</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19" s="12">
         <f>'Данные принтеров'!K14</f>
         <v>72</v>
       </c>
-      <c r="C19" s="6">
-        <f>B19/$B$22</f>
+      <c r="C19" s="15">
+        <f t="shared" si="1"/>
         <v>1.5517241379310345E-2</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="4">
+      <c r="B20" s="12">
         <f>'Данные принтеров'!L14</f>
         <v>12</v>
       </c>
-      <c r="C20" s="6">
-        <f>B20/$B$22</f>
+      <c r="C20" s="15">
+        <f t="shared" si="1"/>
         <v>2.5862068965517241E-3</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="4">
+      <c r="B21" s="12">
         <f>'Данные принтеров'!M14</f>
         <v>12</v>
       </c>
-      <c r="C21" s="6">
-        <f>B21/$B$22</f>
+      <c r="C21" s="15">
+        <f t="shared" si="1"/>
         <v>2.5862068965517241E-3</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="17">
         <f>SUM(B16:B21)</f>
         <v>4640</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="18">
         <f>SUM(C16:C21)</f>
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B23" s="4"/>
+      <c r="B23" s="12"/>
     </row>
     <row r="24" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B24" s="4"/>
+      <c r="B24" s="12"/>
     </row>
     <row r="25" spans="1:8" ht="25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="B25" s="4">
+      <c r="B25" s="12">
         <f>B12-B22</f>
         <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
     </row>
     <row r="27" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
     </row>
     <row r="28" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-      <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1396,7 +1572,8 @@
     <mergeCell ref="A28:H28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1414,46 +1591,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="44" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1464,37 +1641,37 @@
       <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="2">
         <v>3283432.311992785</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>407840.884219317</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>2808645.4923700006</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="3">
         <v>285</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>290</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="3">
         <v>144</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="3">
         <v>124</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="3">
         <v>14</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="3">
         <v>7</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="3">
         <v>0</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="3">
         <v>1</v>
       </c>
       <c r="N2" s="1" t="s">
@@ -1508,37 +1685,37 @@
       <c r="B3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="2">
         <v>5110124.6819955837</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>240826.93712984998</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>3819551.6018210305</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="3">
         <v>289</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3" s="3">
         <v>292</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="3">
         <v>170</v>
       </c>
-      <c r="I3" s="4">
+      <c r="I3" s="3">
         <v>104</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="3">
         <v>14</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="3">
         <v>3</v>
       </c>
-      <c r="L3" s="4">
+      <c r="L3" s="3">
         <v>0</v>
       </c>
-      <c r="M3" s="4">
+      <c r="M3" s="3">
         <v>1</v>
       </c>
       <c r="N3" s="1" t="s">
@@ -1552,37 +1729,37 @@
       <c r="B4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>1342122.3610655204</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>68287.820344211068</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>1323972.5697899801</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="3">
         <v>89</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>88</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="3">
         <v>56</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="3">
         <v>17</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="3">
         <v>11</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="3">
         <v>2</v>
       </c>
-      <c r="L4" s="4">
+      <c r="L4" s="3">
         <v>0</v>
       </c>
-      <c r="M4" s="4">
+      <c r="M4" s="3">
         <v>2</v>
       </c>
       <c r="N4" s="1" t="s">
@@ -1596,37 +1773,37 @@
       <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>2599878.8314560885</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>92067.798591806</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>2608314.967953241</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>222</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="3">
         <v>256</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="3">
         <v>111</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="3">
         <v>69</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>66</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="3">
         <v>10</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="3">
         <v>0</v>
       </c>
-      <c r="M5" s="4">
+      <c r="M5" s="3">
         <v>0</v>
       </c>
       <c r="N5" s="1" t="s">
@@ -1640,37 +1817,37 @@
       <c r="B6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>1285879.780078752</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6" s="2">
         <v>62521.023556879001</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>1678266.1905297909</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>129</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>133</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="3">
         <v>81</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="3">
         <v>41</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="3">
         <v>9</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="3">
         <v>2</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="3">
         <v>0</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6" s="3">
         <v>0</v>
       </c>
       <c r="N6" s="1" t="s">
@@ -1684,37 +1861,37 @@
       <c r="B7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="2">
         <v>12319850.915577138</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7" s="2">
         <v>201447.63243492402</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>9054976.1280580945</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="3">
         <v>1039</v>
       </c>
-      <c r="G7" s="4">
+      <c r="G7" s="3">
         <v>1046</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="3">
         <v>736</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="3">
         <v>257</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="3">
         <v>40</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="3">
         <v>6</v>
       </c>
-      <c r="L7" s="4">
+      <c r="L7" s="3">
         <v>1</v>
       </c>
-      <c r="M7" s="4">
+      <c r="M7" s="3">
         <v>6</v>
       </c>
       <c r="N7" s="1" t="s">
@@ -1728,37 +1905,37 @@
       <c r="B8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="2">
         <v>14764661.29171915</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="2">
         <v>195748.64786772398</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8" s="2">
         <v>10839956.247528652</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="3">
         <v>1459</v>
       </c>
-      <c r="G8" s="4">
+      <c r="G8" s="3">
         <v>1359</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="3">
         <v>921</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="3">
         <v>351</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="3">
         <v>51</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="3">
         <v>31</v>
       </c>
-      <c r="L8" s="4">
+      <c r="L8" s="3">
         <v>3</v>
       </c>
-      <c r="M8" s="4">
+      <c r="M8" s="3">
         <v>2</v>
       </c>
       <c r="N8" s="1" t="s">
@@ -1772,37 +1949,37 @@
       <c r="B9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="2">
         <v>34640.541010587047</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="2">
         <v>12480.125755500048</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="2">
         <v>48226.914519999955</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="3">
         <v>7</v>
       </c>
-      <c r="G9" s="4">
+      <c r="G9" s="3">
         <v>7</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="3">
         <v>6</v>
       </c>
-      <c r="I9" s="4">
+      <c r="I9" s="3">
         <v>1</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="3">
         <v>0</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="3">
         <v>0</v>
       </c>
-      <c r="L9" s="4">
+      <c r="L9" s="3">
         <v>0</v>
       </c>
-      <c r="M9" s="4">
+      <c r="M9" s="3">
         <v>0</v>
       </c>
       <c r="N9" s="1" t="s">
@@ -1816,37 +1993,37 @@
       <c r="B10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="2">
         <v>25351414.54701101</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="2">
         <v>114006.29811895778</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="2">
         <v>19547414.347317189</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="3">
         <v>1119</v>
       </c>
-      <c r="G10" s="4">
+      <c r="G10" s="3">
         <v>1139</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="3">
         <v>825</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="3">
         <v>258</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="3">
         <v>37</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10" s="3">
         <v>11</v>
       </c>
-      <c r="L10" s="4">
+      <c r="L10" s="3">
         <v>8</v>
       </c>
-      <c r="M10" s="4">
+      <c r="M10" s="3">
         <v>0</v>
       </c>
       <c r="N10" s="1" t="s">
@@ -1860,37 +2037,37 @@
       <c r="B11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="2">
         <v>31495.800933186991</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="2">
         <v>7806.7207756810003</v>
       </c>
-      <c r="E11" s="3">
+      <c r="E11" s="2">
         <v>30742.254789999995</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="3">
         <v>29</v>
       </c>
-      <c r="G11" s="4">
+      <c r="G11" s="3">
         <v>30</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="3">
         <v>13</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="3">
         <v>15</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="3">
         <v>2</v>
       </c>
-      <c r="K11" s="4">
+      <c r="K11" s="3">
         <v>0</v>
       </c>
-      <c r="L11" s="4">
+      <c r="L11" s="3">
         <v>0</v>
       </c>
-      <c r="M11" s="4">
+      <c r="M11" s="3">
         <v>0</v>
       </c>
       <c r="N11" s="1" t="s">
@@ -1898,171 +2075,171 @@
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
-      <c r="I12" s="4"/>
-      <c r="J12" s="4"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B14" s="10"/>
-      <c r="C14" s="13">
+      <c r="B14" s="5"/>
+      <c r="C14" s="7">
         <f>SUM(C2:C11)</f>
         <v>66123501.062839806</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D14" s="7">
         <f>MAX(D2:D11)</f>
         <v>407840.884219317</v>
       </c>
-      <c r="E14" s="13">
-        <f>SUM(E2:E11)</f>
+      <c r="E14" s="7">
+        <f t="shared" ref="E14:M14" si="0">SUM(E2:E11)</f>
         <v>51760066.714677982</v>
       </c>
-      <c r="F14" s="11">
-        <f>SUM(F2:F11)</f>
+      <c r="F14" s="6">
+        <f t="shared" si="0"/>
         <v>4667</v>
       </c>
-      <c r="G14" s="11">
-        <f>SUM(G2:G11)</f>
+      <c r="G14" s="6">
+        <f t="shared" si="0"/>
         <v>4640</v>
       </c>
-      <c r="H14" s="11">
-        <f>SUM(H2:H11)</f>
+      <c r="H14" s="6">
+        <f t="shared" si="0"/>
         <v>3063</v>
       </c>
-      <c r="I14" s="11">
-        <f>SUM(I2:I11)</f>
+      <c r="I14" s="6">
+        <f t="shared" si="0"/>
         <v>1237</v>
       </c>
-      <c r="J14" s="11">
-        <f>SUM(J2:J11)</f>
+      <c r="J14" s="6">
+        <f t="shared" si="0"/>
         <v>244</v>
       </c>
-      <c r="K14" s="11">
-        <f>SUM(K2:K11)</f>
+      <c r="K14" s="6">
+        <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="L14" s="11">
-        <f>SUM(L2:L11)</f>
+      <c r="L14" s="6">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="M14" s="11">
-        <f>SUM(M2:M11)</f>
+      <c r="M14" s="6">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="N14" s="10"/>
+      <c r="N14" s="5"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="8"/>
+      <c r="H16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8"/>
+      <c r="H17" s="8"/>
+      <c r="I17" s="8"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="8"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="8"/>
+      <c r="I19" s="8"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="5">
